--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_339_R34.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_339_R34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6839</v>
+        <v>4.8127</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7636</v>
+        <v>4.8252</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0124</v>
       </c>
       <c r="G2" t="n">
         <v>3.5824</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1125</v>
+        <v>1.0163</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4991</v>
+        <v>0.5625</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3866</v>
+        <v>0.4538</v>
       </c>
       <c r="V2" t="n">
         <v>0.6778999999999999</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. LESSORT</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9547</v>
+        <v>1.8029</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4353</v>
+        <v>1.5729</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5194</v>
+        <v>0.23</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5592</v>
+        <v>1.2048</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3878</v>
+        <v>0.7296</v>
       </c>
       <c r="I3" t="n">
-        <v>0.947</v>
+        <v>0.4752</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0466</v>
+        <v>3.3425</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2001</v>
+        <v>2.1279</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8465</v>
+        <v>1.2146</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4874</v>
+        <v>-2.1377</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5879</v>
+        <v>-1.3983</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1005</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.232</v>
+        <v>0.232</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6274</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>1.172</v>
+        <v>-0.4991</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4554</v>
+        <v>0.5816</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5361</v>
+        <v>-0.1107</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5361</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>M. LESSORT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2307</v>
+        <v>1.7161</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1328</v>
+        <v>0.5663</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9021</v>
+        <v>1.1498</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3905</v>
+        <v>0.5592</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2724</v>
+        <v>-0.3878</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6629</v>
+        <v>0.947</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3999</v>
+        <v>2.0466</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3263</v>
+        <v>1.2001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0736</v>
+        <v>0.8465</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7904</v>
+        <v>-1.4874</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0539</v>
+        <v>-1.5879</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7365</v>
+        <v>0.1005</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R4" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0129</v>
+        <v>1.3888</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3566</v>
+        <v>0.3031</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6563</v>
+        <v>1.0857</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6083</v>
+        <v>0.5361</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8053</v>
+        <v>1.3048</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0936</v>
+        <v>2.543</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2883</v>
+        <v>-1.2382</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2758</v>
+        <v>-1.3905</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8355</v>
+        <v>0.2724</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1113</v>
+        <v>-1.6629</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4013</v>
+        <v>0.3999</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7728</v>
+        <v>0.3263</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3716</v>
+        <v>0.0736</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.677</v>
+        <v>-1.7904</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9373</v>
+        <v>-0.0539</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7398</v>
+        <v>-1.7365</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>1.759</v>
+        <v>1.087</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9243</v>
+        <v>0.7668</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8347</v>
+        <v>0.3203</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1418</v>
+        <v>1.6083</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GRIGONIS</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4755</v>
+        <v>1.2573</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8135</v>
+        <v>2.8144</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3381</v>
+        <v>-1.5571</v>
       </c>
       <c r="G6" t="n">
-        <v>1.362</v>
+        <v>-0.2758</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1475</v>
+        <v>1.8355</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5095</v>
+        <v>-2.1113</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5237</v>
+        <v>2.4013</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5679</v>
+        <v>2.7728</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0916</v>
+        <v>-0.3716</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1617</v>
+        <v>-2.677</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5796</v>
+        <v>-0.9373</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5821</v>
+        <v>-1.7398</v>
       </c>
       <c r="P6" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R6" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>1.6316</v>
+        <v>1.2109</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2898</v>
+        <v>0.6451</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3418</v>
+        <v>0.5658</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7501</v>
+        <v>-0.1418</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7501</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. HAYES-DAVIS</t>
+          <t>M. GRIGONIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3391</v>
+        <v>1.0036</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5954</v>
+        <v>3.3417</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2563</v>
+        <v>-2.3381</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2856</v>
+        <v>1.362</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1225</v>
+        <v>-1.1475</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8369</v>
+        <v>2.5095</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3511</v>
+        <v>2.5237</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8599</v>
+        <v>-0.5679</v>
       </c>
       <c r="L7" t="n">
-        <v>1.211</v>
+        <v>3.0916</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6368</v>
+        <v>-1.1617</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2626</v>
+        <v>-0.5796</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6258</v>
+        <v>-0.5821</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2151</v>
+        <v>1.1598</v>
       </c>
       <c r="T7" t="n">
-        <v>1.172</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0431</v>
+        <v>0.3418</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.214</v>
+        <v>-1.7501</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2862</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>N. HAYES-DAVIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3162</v>
+        <v>0.8809</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9517</v>
+        <v>1.8011</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3644</v>
+        <v>-0.9202</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2048</v>
+        <v>-0.2856</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7296</v>
+        <v>-2.1225</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4752</v>
+        <v>1.8369</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3425</v>
+        <v>0.3511</v>
       </c>
       <c r="K8" t="n">
-        <v>2.1279</v>
+        <v>-0.8599</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2146</v>
+        <v>1.211</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1377</v>
+        <v>-0.6368</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3983</v>
+        <v>-1.2626</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0.6258</v>
       </c>
       <c r="P8" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4042</v>
+        <v>0.7569</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1202</v>
+        <v>0.3778</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7161</v>
+        <v>0.3791</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2836</v>
+        <v>-1.214</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1107</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3943</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2901</v>
+        <v>0.2489</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0412</v>
+        <v>0.4306</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.249</v>
+        <v>-0.1817</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1109</v>
@@ -1156,13 +1156,13 @@
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0527</v>
+        <v>0.5917</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0668</v>
+        <v>0.405</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1195</v>
+        <v>0.1867</v>
       </c>
       <c r="V9" t="n">
         <v>0.5361</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6683</v>
+        <v>-2.6775</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2045</v>
+        <v>-0.5833</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4638</v>
+        <v>-2.0942</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3305</v>
@@ -1234,13 +1234,13 @@
         <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5671</v>
+        <v>0.4237</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7662</v>
+        <v>-0.145</v>
       </c>
       <c r="U10" t="n">
-        <v>0.199</v>
+        <v>0.5687</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4665</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8645</v>
+        <v>-3.6207</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8094</v>
+        <v>-3.8344</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0551</v>
+        <v>0.2137</v>
       </c>
       <c r="G11" t="n">
         <v>-4.6039</v>
@@ -1312,13 +1312,13 @@
         <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0983</v>
+        <v>0.1456</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3364</v>
+        <v>-0.3613</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2381</v>
+        <v>0.507</v>
       </c>
       <c r="V11" t="n">
         <v>0.1418</v>
@@ -1345,28 +1345,28 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.9825</v>
+        <v>6.729000000000003</v>
       </c>
       <c r="E12" t="n">
-        <v>12.7308</v>
+        <v>13.4775</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.7486</v>
+        <v>-6.748399999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.288800000000001</v>
+        <v>-3.2888</v>
       </c>
       <c r="H12" t="n">
         <v>-3.0376</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2512000000000005</v>
+        <v>-0.2512000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>13.5835</v>
       </c>
       <c r="K12" t="n">
-        <v>6.959700000000001</v>
+        <v>6.959699999999999</v>
       </c>
       <c r="L12" t="n">
         <v>6.6236</v>
@@ -1375,7 +1375,7 @@
         <v>-16.8723</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.997400000000001</v>
+        <v>-9.997399999999999</v>
       </c>
       <c r="O12" t="n">
         <v>-6.8749</v>
@@ -1390,19 +1390,19 @@
         <v>11.5979</v>
       </c>
       <c r="S12" t="n">
-        <v>7.1166</v>
+        <v>7.863300000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>2.126</v>
+        <v>2.8729</v>
       </c>
       <c r="U12" t="n">
-        <v>4.9906</v>
+        <v>4.9905</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3247</v>
       </c>
       <c r="W12" t="n">
-        <v>5.139600000000001</v>
+        <v>5.1396</v>
       </c>
       <c r="X12" t="n">
         <v>-6.4643</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.296099999999999</v>
+        <v>10.8281</v>
       </c>
       <c r="E13" t="n">
-        <v>11.5589</v>
+        <v>12.1487</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2629</v>
+        <v>-1.3206</v>
       </c>
       <c r="G13" t="n">
         <v>10.1292</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3872</v>
+        <v>-0.8551</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2617</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1255</v>
+        <v>-0.1832</v>
       </c>
       <c r="V13" t="n">
         <v>0.3943</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>M. STRAZEL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9454</v>
+        <v>1.2935</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1451</v>
+        <v>0.033</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8004</v>
+        <v>1.2604</v>
       </c>
       <c r="G14" t="n">
-        <v>1.77</v>
+        <v>2.3086</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0133</v>
+        <v>1.9773</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7567</v>
+        <v>0.3314</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8093</v>
+        <v>3.4669</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6253</v>
+        <v>2.3394</v>
       </c>
       <c r="L14" t="n">
-        <v>0.184</v>
+        <v>1.1275</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9607</v>
+        <v>-1.1582</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.612</v>
+        <v>-0.3621</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5727</v>
+        <v>-0.7961</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1598</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.376</v>
+        <v>-0.7009</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6642</v>
+        <v>-0.9392</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2882</v>
+        <v>0.2383</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.6083</v>
+        <v>2.933</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.6083</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. STRAZEL</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5636</v>
+        <v>0.9518</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4388</v>
+        <v>0.263</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0023</v>
+        <v>0.6888</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3086</v>
+        <v>1.77</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9773</v>
+        <v>0.0133</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3314</v>
+        <v>1.7567</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4669</v>
+        <v>0.8093</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3394</v>
+        <v>0.6253</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1275</v>
+        <v>0.184</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1582</v>
+        <v>0.9607</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3621</v>
+        <v>-0.612</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7961</v>
+        <v>1.5727</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.2473</v>
+        <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4308</v>
+        <v>-0.3697</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.411</v>
+        <v>-0.5463</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0198</v>
+        <v>0.1766</v>
       </c>
       <c r="V15" t="n">
-        <v>2.933</v>
+        <v>-1.6083</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7886</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7843</v>
+        <v>-0.9917</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.2183</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3565</v>
+        <v>-1.2099</v>
       </c>
       <c r="G16" t="n">
         <v>0.4518</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.293</v>
+        <v>-0.5004</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0395</v>
+        <v>-0.3143</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3325</v>
+        <v>-0.186</v>
       </c>
       <c r="V16" t="n">
         <v>1.6083</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7861</v>
+        <v>-1.6173</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2184</v>
+        <v>-1.6515</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5677</v>
+        <v>0.0342</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.969</v>
+        <v>-1.8562</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5809</v>
+        <v>2.353</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.55</v>
+        <v>-4.2092</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1041</v>
+        <v>0.4564</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2791</v>
+        <v>3.3442</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.175</v>
+        <v>-2.8877</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0732</v>
+        <v>-2.3126</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6982</v>
+        <v>-0.9912</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.375</v>
+        <v>-1.3215</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2937</v>
+        <v>-0.2998</v>
       </c>
       <c r="T17" t="n">
-        <v>0.948</v>
+        <v>-0.8606</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3457</v>
+        <v>0.5608</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1107</v>
+        <v>1.4665</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.1107</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7739</v>
+        <v>-2.0042</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4156</v>
+        <v>-1.5158</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3584</v>
+        <v>-0.4884</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8562</v>
+        <v>-1.969</v>
       </c>
       <c r="H18" t="n">
-        <v>2.353</v>
+        <v>1.5809</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.2092</v>
+        <v>-3.55</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4564</v>
+        <v>0.1041</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3442</v>
+        <v>2.2791</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.8877</v>
+        <v>-2.175</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3126</v>
+        <v>-2.0732</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9912</v>
+        <v>-0.6982</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3215</v>
+        <v>-1.375</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4564</v>
+        <v>0.0756</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6247</v>
+        <v>-0.3495</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1683</v>
+        <v>0.425</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4665</v>
+        <v>-0.1107</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>-0.1107</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2237</v>
+        <v>-2.7969</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.259</v>
+        <v>-1.0231</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9647</v>
+        <v>-1.7738</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1714</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5162</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.224</v>
+        <v>0.0119</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2921</v>
+        <v>-0.1013</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5361</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7026</v>
+        <v>-3.5726</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.593</v>
+        <v>-1.4751</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1096</v>
+        <v>-2.0975</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8506</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2437</v>
+        <v>-1.1136</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7468</v>
+        <v>-0.6289</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4968</v>
+        <v>-0.4848</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.5168</v>
+        <v>-5.714</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7448</v>
+        <v>-0.3909</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.7721</v>
+        <v>-5.3231</v>
       </c>
       <c r="G21" t="n">
         <v>-3.5235</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7071</v>
+        <v>-0.9043</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0455</v>
+        <v>-0.6917</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6616</v>
+        <v>-0.2126</v>
       </c>
       <c r="V21" t="n">
         <v>-1.7501</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.982300000000002</v>
+        <v>-3.6233</v>
       </c>
       <c r="E22" t="n">
-        <v>6.6065</v>
+        <v>6.606599999999998</v>
       </c>
       <c r="F22" t="n">
-        <v>-12.5892</v>
+        <v>-10.2299</v>
       </c>
       <c r="G22" t="n">
         <v>3.2889</v>
       </c>
       <c r="H22" t="n">
-        <v>3.0375</v>
+        <v>3.037500000000001</v>
       </c>
       <c r="I22" t="n">
         <v>0.2512000000000008</v>
@@ -2170,13 +2170,13 @@
         <v>8.118399999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>-7.1167</v>
+        <v>-4.7576</v>
       </c>
       <c r="T22" t="n">
-        <v>-4.990399999999999</v>
+        <v>-4.9905</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.1261</v>
+        <v>0.2328</v>
       </c>
       <c r="V22" t="n">
         <v>1.3247</v>
